--- a/model/ABNB_margin_model.xlsx
+++ b/model/ABNB_margin_model.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ABNB margin model — WS23 final</t>
+          <t>ABNB margin model — WS23 final, post-audit (WS31)</t>
         </is>
       </c>
     </row>
@@ -493,115 +493,115 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>What this workbook is</t>
+          <t>THIS IS A FROZEN REPORT, NOT AN INPUT-DRIVEN MODEL.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A margin model on top of an adopted revenue path. It does NOT forecast revenue.</t>
+          <t>Every forecast cell is a value generated from the CSVs in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The adj EBITDA margin for 3Q26 comes from final-margin|combined|stack_clip, a</t>
+          <t>data/processed/margin_build/23_final_model/. Changing a number on the Inputs sheet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>six-member leave-future-out combination plus a zero-parameter management-sentence clip.</t>
+          <t>does NOT flow through: the only live formulas are the local identities on the Bridge</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4Q26 comes from the Street baseline (the combination loses to it at h=1).</t>
+          <t>sheet (line sum, total cash costs, adj EBITDA, margins, operating income, pretax,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027 is a SCENARIO: the combination fails its test at h&gt;=2.</t>
+          <t>tax, net income, EPS), and their cached results are blank until Excel opens the file</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FY28 is the FY27 margin rolled flat — an extrapolation, not a forecast.</t>
+          <t>and recalculates. To change an assumption, edit the code and rebuild:</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    py -3.13 analysis/src/margin_build/23_final_model/run.py</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Sheets</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(MARGIN_VERIFY_ONLY=1 recomputes into _verify/ and compares, writing nothing.)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Inputs      revenue path, model parameters, sources</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lines       six cash cost lines, history 1Q21-2Q26 and forecast 3Q26-4Q27</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>What this workbook is</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bridge      adj EBITDA -&gt; operating income -&gt; EPS -&gt; FCF, quarterly and annual</t>
+          <t>A margin model on top of an adopted revenue path. It does NOT forecast revenue.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scenarios   bear/base/bull revenue x cost-response variant (M6 k), macro sensitivity, FY26 floor</t>
+          <t>The adj EBITDA margin for 3Q26 comes from final-margin|combined|stack_clip, a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Consensus   model vs LSEG / Bloomberg / management, with n and dispersion</t>
+          <t>six-member leave-future-out combination plus a zero-parameter management-sentence clip.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Seasonality quarterly profile with the mechanical / discretionary cost split</t>
+          <t>4Q26 comes from the Street baseline (the combination loses to it at h=1).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Weights     the combination's member weights, backtest scores and diagnostics</t>
+          <t>2027 is a SCENARIO: the combination fails its test at h&gt;=2.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Card        the 5 Nov card and the FY-guide budget identity</t>
+          <t>FY28 is the FY27 margin rolled flat — an extrapolation, not a forecast.</t>
         </is>
       </c>
     </row>
@@ -611,57 +611,123 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Every forecast number is in data/processed/margin_build/23_final_model/*.csv.</t>
+          <t>Inputs      revenue path, model parameters, sources</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rebuild: py -3.13 analysis/src/margin_build/23_final_model/run.py</t>
+          <t>Lines       six cash cost lines, history 1Q21-2Q26 and forecast 3Q26-4Q27</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bridge      adj EBITDA -&gt; operating income -&gt; EPS -&gt; FCF, quarterly and annual</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Numbers that must NOT be quoted (kill list, AGENT_BRIEF §6 + WS21 addendum + WS22)</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Scenarios   bear/base/bull revenue x cost-response variant (M6 k), macro sensitivity, FY26 floor</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>M3 LIVE 4Q26 34.51% / FY26 37.03%; M6 FY28 31.3%; M5 '+0.41pt beat' as a model output;</t>
+          <t>Consensus   model vs LSEG / Bloomberg / management, with n and dispersion</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>M1 d_steps_rw; any oracle spec; 'survives both windows' as evidence of skill;</t>
+          <t>Seasonality quarterly profile with the mechanical / discretionary cost split</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>any margin MAE ratio without its p-value and quarters-better count;</t>
+          <t>Weights     the combination's member weights, backtest scores and diagnostics</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Card        the 5 Nov card and the FY-guide budget identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Traceability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Every forecast number is in data/processed/margin_build/23_final_model/*.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rebuild: py -3.13 analysis/src/margin_build/23_final_model/run.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Numbers that must NOT be quoted (kill list, AGENT_BRIEF §6 + WS21 addendum + WS22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>M3 LIVE 4Q26 34.51% / FY26 37.03%; M6 FY28 31.3%; M5 '+0.41pt beat' as a model output;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>M1 d_steps_rw; any oracle spec; 'survives both windows' as evidence of skill;</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>any margin MAE ratio without its p-value and quarters-better count;</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>any quarterly FCF forecast; 'M7 tax quantiles under-cover'.</t>
         </is>
@@ -678,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -687,12 +753,13 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1455,12 +1522,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>attainable_cov80_lo</t>
+          <t>rank_grid_cov80_lo</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>attainable_cov80_hi</t>
+          <t>rank_grid_cov80_hi</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1470,15 +1537,20 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>gaussian_sd_from_qhat80</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>bias</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>bias_last5</t>
         </is>
@@ -1517,12 +1589,15 @@
         <v>1.809296095507047</v>
       </c>
       <c r="J45" s="4" t="n">
+        <v>1.719680993963964</v>
+      </c>
+      <c r="K45" s="4" t="n">
         <v>1.126424550987544</v>
       </c>
-      <c r="K45" s="4" t="n">
+      <c r="L45" s="4" t="n">
         <v>-0.6693158605443091</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>-0.2712741759064897</v>
       </c>
     </row>
@@ -1559,12 +1634,15 @@
         <v>1.29706912222906</v>
       </c>
       <c r="J46" s="4" t="n">
+        <v>1.623177835578563</v>
+      </c>
+      <c r="K46" s="4" t="n">
         <v>0.8075242671638136</v>
       </c>
-      <c r="K46" s="4" t="n">
+      <c r="L46" s="4" t="n">
         <v>-0.4845417318349625</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="M46" s="4" t="n">
         <v>-0.2712741759064897</v>
       </c>
     </row>
@@ -1598,16 +1676,19 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3.151829325919671</v>
+        <v>3.135332398978297</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.962253686422446</v>
+        <v>3.281155324664941</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-0.4420676195151281</v>
+        <v>1.951983093583188</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>-0.4314516350688187</v>
+        <v>-0.450166606954569</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>-0.4294982970542129</v>
       </c>
     </row>
     <row r="48">
@@ -1628,7 +1709,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2.599850651335565</v>
+        <v>2.416179191000801</v>
       </c>
       <c r="F48" s="4" t="n">
         <v>4.205128664090589</v>
@@ -1640,16 +1721,19 @@
         <v>0.9090909090909092</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.531684806574287</v>
+        <v>2.510238801550501</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.576166515016018</v>
+        <v>1.885283388733458</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-0.193713144534883</v>
+        <v>1.562814744324982</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>-0.4314516350688187</v>
+        <v>-0.2042418282061563</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>-0.4294982970542129</v>
       </c>
     </row>
     <row r="49">
@@ -1682,16 +1766,19 @@
         <v>0.9230769230769232</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>3.622641899965389</v>
+        <v>3.580195245064639</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>2.255370354078833</v>
+        <v>3.529123061089033</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-0.4615550173883957</v>
+        <v>2.228944080178042</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>-0.4861938659977397</v>
+        <v>-0.442768154280881</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>-0.4416929905982655</v>
       </c>
     </row>
     <row r="50">
@@ -1712,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3.88847717484494</v>
+        <v>3.650223179771114</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>4.547336566744603</v>
@@ -1724,16 +1811,19 @@
         <v>0.9090909090909092</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.250363101949208</v>
+        <v>3.199427116068308</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>2.023598462822946</v>
+        <v>2.848176638398185</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.128979941205578</v>
+        <v>1.991886934141997</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>-0.4861938659977397</v>
+        <v>0.1515241769345957</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>-0.4416929905982655</v>
       </c>
     </row>
     <row r="51">
@@ -1769,12 +1859,15 @@
         <v>63.74173131409582</v>
       </c>
       <c r="J51" s="4" t="n">
+        <v>59.56127811796059</v>
+      </c>
+      <c r="K51" s="4" t="n">
         <v>39.6840800424805</v>
       </c>
-      <c r="K51" s="4" t="n">
+      <c r="L51" s="4" t="n">
         <v>-13.94472240806033</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>-9.800419846978082</v>
       </c>
     </row>
@@ -1811,12 +1904,15 @@
         <v>49.93604664601964</v>
       </c>
       <c r="J52" s="4" t="n">
+        <v>51.95427240404968</v>
+      </c>
+      <c r="K52" s="4" t="n">
         <v>31.08899038748667</v>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="L52" s="4" t="n">
         <v>-9.812088593339359</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <v>-9.800419846978082</v>
       </c>
     </row>
@@ -1838,10 +1934,10 @@
         <v>13</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>112.2115426740384</v>
+        <v>107.5548578275793</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>164.0576934581486</v>
+        <v>170.651235835543</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>0.8571428571428571</v>
@@ -1850,16 +1946,19 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>120.9377256457187</v>
+        <v>121.2208152706159</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>75.29294052323506</v>
+        <v>83.92232976558935</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-6.458075237173879</v>
+        <v>75.46918536475431</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>-43.98410438909718</v>
+        <v>-6.198149854358816</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>-43.7838006314397</v>
       </c>
     </row>
     <row r="54">
@@ -1880,10 +1979,10 @@
         <v>10</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>112.2115426740384</v>
+        <v>107.5548578275793</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>164.0576934581486</v>
+        <v>170.651235835543</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>0.8181818181818182</v>
@@ -1892,16 +1991,19 @@
         <v>0.9090909090909092</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>115.0770739572769</v>
+        <v>115.4450904696432</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>71.64423870873334</v>
+        <v>83.92232976558935</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-1.5344411458842</v>
+        <v>71.87335700270836</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>-43.98410438909718</v>
+        <v>-1.196538148224619</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>-43.7838006314397</v>
       </c>
     </row>
     <row r="55">
@@ -1922,10 +2024,10 @@
         <v>12</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>149.6220884698005</v>
+        <v>150.0974018505301</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>177.4147364388809</v>
+        <v>180.7583249605468</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>0.8461538461538461</v>
@@ -1934,16 +2036,19 @@
         <v>0.9230769230769232</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>137.7975118390509</v>
+        <v>138.7555141189085</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>85.78944086927048</v>
+        <v>117.117198697355</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>8.66068460655022</v>
+        <v>86.38587021580661</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>-39.71571444889155</v>
+        <v>10.09226734645174</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>-38.80704159307409</v>
       </c>
     </row>
     <row r="56">
@@ -1964,10 +2069,10 @@
         <v>10</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>149.6220884698005</v>
+        <v>150.0974018505301</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>177.4147364388809</v>
+        <v>180.7583249605468</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>0.8181818181818182</v>
@@ -1976,16 +2081,289 @@
         <v>0.9090909090909092</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>149.9808900133822</v>
+        <v>151.1304927492112</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>93.37452123484024</v>
+        <v>117.117198697355</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>16.65884067004545</v>
+        <v>94.09023645068358</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>-39.71571444889155</v>
+        <v>18.37673995792728</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>-38.80704159307409</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>W1_all_n14</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>62.58378500133336</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>89.94124822969684</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>49.23957748880937</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>48.83254135559719</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>30.655385318844</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>-11.46619280784791</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>-4.963008497922861</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>recent_2024Q1plus</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>62.58378500133336</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>68.88488192096918</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>42.89792615616632</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>48.83254135559719</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>26.70722461002972</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>-6.124364846733482</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>-4.963008497922861</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>W1_all_n14</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>119.8042280899093</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>193.15460207259</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>125.7606268392008</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>93.4802029415647</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>78.29556365651661</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>1.154825090442942</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>-43.70823322077003</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>recent_2024Q1plus</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>118.3635687682455</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>193.15460207259</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>123.4918987121797</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>92.35609298396184</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>76.88310769193527</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>2.441552061130269</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>-43.70823322077003</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>W1_all_n14</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>149.4899145957761</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>180.7583249605464</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>0.9230769230769232</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>138.065949701514</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>116.6431917882148</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>85.95656387331825</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>10.65983240194402</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>-37.48441339222855</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>adj_ebitda_musd_from_margin</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>recent_2024Q1plus</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>149.4899145957761</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>180.7583249605464</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>150.3030154483378</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>116.6431917882148</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>93.57506883969752</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>19.05781802451797</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>-37.48441339222855</v>
       </c>
     </row>
   </sheetData>
@@ -1999,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2010,11 +2388,14 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2874,27 +3255,42 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>other_net_musd</t>
+          <t>sum_five_lines_musd</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>addbacks_musd</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>residual_allocated_musd</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>total_cash_costs_musd</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>recon_gap_musd</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>adj_ebitda_musd</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>adj_ebitda_margin_pct</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>scenario_cost_basis</t>
         </is>
       </c>
     </row>
@@ -2919,28 +3315,39 @@
         <v>364.80540374915</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>382.1317787366347</v>
+        <v>381.0150238529766</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>790.2398152649166</v>
+        <v>781.1389859657324</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>282.8162050025537</v>
+        <v>281.1527755386359</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32.51498424666773</v>
+        <v>2425.537068211465</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>78.54057788414593</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K28" s="4" t="n">
+        <v>66.65956423738589</v>
+      </c>
+      <c r="L28" s="4" t="n">
         <v>2404.903097611558</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="M28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>2399.132402388442</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>49.93993908638773</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2964,28 +3371,39 @@
         <v>318.2894504254017</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>375.7219392474648</v>
+        <v>375.6395710821145</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>771.2996576642566</v>
+        <v>770.6284104429461</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>272.0314129763893</v>
+        <v>271.9087238929229</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21.51027507003473</v>
+        <v>2280.350071302822</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-13.59830319867206</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K29" s="4" t="n">
+        <v>-14.47460766879931</v>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>2259.716100702914</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="M29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n">
         <v>918.391699297086</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>28.897437</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -3009,28 +3427,39 @@
         <v>316.380655663393</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>421.980478094075</v>
+        <v>421.9776190609413</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>857.9924216597727</v>
+        <v>857.9691223907109</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>238.9808310788453</v>
+        <v>238.9765724899441</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>20.66438749100411</v>
+        <v>2479.312230042951</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3677976161216065</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K30" s="4" t="n">
+        <v>-0.3982145072181993</v>
+      </c>
+      <c r="L30" s="4" t="n">
         <v>2458.678259443044</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="M30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n">
         <v>594.4510405569569</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>19.47022160368239</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3054,28 +3483,39 @@
         <v>334.0450646878938</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>422.2037337233075</v>
+        <v>421.5800551253174</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>998.4866996564672</v>
+        <v>993.404122861038</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>242.0473071245772</v>
+        <v>241.1183249718299</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>27.26920814607393</v>
+        <v>2678.315036506585</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.98009635947574</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K31" s="4" t="n">
+        <v>7.344858813309202</v>
+      </c>
+      <c r="L31" s="4" t="n">
         <v>2657.681065906678</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n">
         <v>1371.299634093322</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="O31" s="4" t="n">
         <v>34.03589483795052</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -3099,28 +3539,39 @@
         <v>378.0824832694792</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>433.0236610262107</v>
+        <v>431.6036398623501</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>978.666306104484</v>
+        <v>967.0940529604534</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>304.3121731691063</v>
+        <v>302.1970223173678</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>35.74139575953723</v>
+        <v>2750.602473103657</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>120.1200205225059</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K32" s="4" t="n">
+        <v>105.0125953628762</v>
+      </c>
+      <c r="L32" s="4" t="n">
         <v>2729.96850250375</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="M32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n">
         <v>2550.76399749625</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>48.30322303764203</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -3144,28 +3595,39 @@
         <v>329.4369335539894</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>419.1639305686859</v>
+        <v>418.8985605046918</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>904.6316065250904</v>
+        <v>902.469012307805</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>282.1322767278143</v>
+        <v>281.737002536719</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>23.45720907228237</v>
+        <v>2519.582937950812</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-54.27942539117521</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K33" s="4" t="n">
+        <v>-57.10266386354988</v>
+      </c>
+      <c r="L33" s="4" t="n">
         <v>2498.948967350904</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="M33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="n">
         <v>966.8151326490954</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="O33" s="4" t="n">
         <v>27.89616098363692</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>adopted margin path</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -3189,28 +3651,39 @@
         <v>361.274873526688</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>381.644675828227</v>
+        <v>382.0261678139928</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>783.1424187414528</v>
+        <v>786.2513314422317</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>282.0906551601825</v>
+        <v>282.6588953520612</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>32.18309899935274</v>
+        <v>2416.59764032004</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>73.35835178703564</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2380.355896442264</v>
+        <v>77.41699666545901</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2374.644103557736</v>
+        <v>2395.963669720132</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>49.93993908638773</v>
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>2359.036330279868</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>49.61169990073329</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3234,28 +3707,39 @@
         <v>318.0194939368866</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>373.2338728085202</v>
+        <v>375.4935132305229</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>745.4061583746096</v>
+        <v>763.8207648913249</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>268.3253866287196</v>
+        <v>271.6911677063961</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21.14275287820633</v>
+        <v>2266.289621068011</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-40.06852665390034</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2221.10684017341</v>
+        <v>-16.02849863750589</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>902.70015982659</v>
+        <v>2245.655650468103</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>28.897437</v>
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>878.1513495318964</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>28.11157505991556</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3279,28 +3763,39 @@
         <v>308.5343713625237</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>422.4089739505848</v>
+        <v>425.2328120077115</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>854.6271856388508</v>
+        <v>877.6396376124371</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>239.6190845069838</v>
+        <v>243.8252496147381</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20.27205554782092</v>
+        <v>2462.312556665008</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>4.190915484909965</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2411.99804597872</v>
+        <v>34.23337062337714</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>583.1648540212799</v>
+        <v>2441.6785860651</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>19.47022160368239</v>
+        <v>0</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>553.4843139348995</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>18.47927249415715</v>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3324,28 +3819,39 @@
         <v>327.0166313325761</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>414.2487158732226</v>
+        <v>422.6486678703357</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>910.1603804647332</v>
+        <v>978.6145509955636</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>230.1981437392529</v>
+        <v>242.7100457259482</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>25.74461048157816</v>
+        <v>2624.203068466227</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>-70.65233016503316</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2509.09243347001</v>
+        <v>18.71369434960525</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>1294.63146652999</v>
+        <v>2603.569097866319</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>34.03589483795052</v>
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>1200.154802133681</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>31.55210088023688</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3369,28 +3875,39 @@
         <v>366.7949985087064</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>423.5019007600591</v>
+        <v>432.9351946217909</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>876.410747419989</v>
+        <v>953.2859851475794</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>290.1293145965999</v>
+        <v>304.180400632597</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>33.41179624985632</v>
+        <v>2685.802453397222</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>18.81922003461523</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2552.031039522046</v>
+        <v>119.1788376599343</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>2384.506960477953</v>
+        <v>2665.168482797314</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>48.30322303764203</v>
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>2271.369517202685</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>46.0113852502034</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3414,28 +3931,39 @@
         <v>322.6925998696844</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>407.5707551281334</v>
+        <v>418.3624018199534</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>780.6280269406019</v>
+        <v>868.5729608169149</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>264.8640024714128</v>
+        <v>280.938383102338</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21.74581948290669</v>
+        <v>2453.187585888044</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>-177.6177493457631</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2316.630805206079</v>
+        <v>-62.806788146705</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>896.2782947939203</v>
+        <v>2432.553615288137</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>27.89616098363692</v>
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>780.355484711863</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>24.28812831062861</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3459,28 +3987,39 @@
         <v>367.6173183237593</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>383.8354382040923</v>
+        <v>380.4587475479121</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>808.8065794423092</v>
+        <v>781.288736710891</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>285.3538409655761</v>
+        <v>280.3241904932833</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>33.01559556652843</v>
+        <v>2439.021183072644</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>96.66559500159384</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2441.929771366007</v>
+        <v>60.74141114170288</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>2436.070228633993</v>
+        <v>2418.387212472737</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>49.93993908638773</v>
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>2459.612787527263</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>50.4225663699726</v>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3504,28 +4043,39 @@
         <v>319.9522854214302</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>377.5901287952289</v>
+        <v>375.3586306447311</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>791.6300340124019</v>
+        <v>773.4447687887543</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>274.8141198921224</v>
+        <v>271.4902573090843</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>21.84752958179476</v>
+        <v>2293.252558239669</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>6.277128587230891</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2295.145654615058</v>
+        <v>-17.46349736995262</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>932.790945384942</v>
+        <v>2272.618587639762</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>28.897437</v>
+        <v>0</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>955.3180123602384</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>29.59531523513313</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3549,28 +4099,39 @@
         <v>321.5455377087953</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>423.58086401856</v>
+        <v>420.3201378897427</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>878.8444319043766</v>
+        <v>852.2716249939202</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>241.3646389666671</v>
+        <v>236.5077200529353</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21.11656375449064</v>
+        <v>2498.904947184876</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>16.65850536865219</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2512.47883538339</v>
+        <v>-18.03194658435314</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>607.4587646166099</v>
+        <v>2478.270976584968</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>19.47022160368239</v>
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>641.6666234150325</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>20.56664926295425</v>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3594,28 +4155,39 @@
         <v>340.9756419242195</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>427.1665166533505</v>
+        <v>420.0963066013587</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1055.252906642833</v>
+        <v>997.6352720713284</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>249.4394747968786</v>
+        <v>238.9082509010428</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>28.35838912431601</v>
+        <v>2716.972924851374</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>66.77851486704321</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2763.83360424639</v>
+        <v>-8.440553652289054</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>1426.07179575361</v>
+        <v>2696.338954251466</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>34.03589483795052</v>
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>1493.566445748534</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>35.64678204306316</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3639,28 +4211,39 @@
         <v>387.7053030574305</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>440.2954314844473</v>
+        <v>430.0710554411981</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1057.251913332258</v>
+        <v>973.9298679828968</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>315.1436254529373</v>
+        <v>299.9142061690873</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>37.63119816200285</v>
+        <v>2803.169119178294</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>197.4834646539643</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2874.313761692752</v>
+        <v>88.70762397750377</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>2685.633938307248</v>
+        <v>2782.535148578386</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>48.30322303764203</v>
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>2777.412551421613</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>49.95393304547836</v>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3684,28 +4267,39 @@
         <v>337.1677531299605</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>429.4545416627294</v>
+        <v>418.9046745455631</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1014.852145636268</v>
+        <v>928.8775587619266</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>297.4603544877968</v>
+        <v>281.7461095268721</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>25.04902914251139</v>
+        <v>2581.3394512775</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>55.20108159469328</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2668.529121087421</v>
+        <v>-57.03761735773924</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>1032.423778912579</v>
+        <v>2560.705480677592</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>27.89616098363692</v>
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>1140.247419322408</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>30.80956310798789</v>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>flex k=0.364173 on total cash costs (M6)</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3770,13 +4364,13 @@
         <v>7.593728309233977</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>7.954391234965576</v>
+        <v>7.931145051966759</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>16.44949991033407</v>
+        <v>16.2600585687956</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>5.887054852166553</v>
+        <v>5.852429182478688</v>
       </c>
     </row>
     <row r="50">
@@ -3797,13 +4391,13 @@
         <v>10.01506149116156</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>11.82218989700301</v>
+        <v>11.81959816095962</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>24.26914712157519</v>
+        <v>24.2480261507475</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>8.559540144496964</v>
+        <v>8.55567970013235</v>
       </c>
     </row>
     <row r="51">
@@ -3824,13 +4418,13 @@
         <v>10.36250432182459</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.82124491399938</v>
+        <v>13.82115127128554</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>28.10206635073637</v>
+        <v>28.10130322324413</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>7.827406165826169</v>
+        <v>7.827266683069864</v>
       </c>
     </row>
     <row r="52">
@@ -3851,13 +4445,13 @@
         <v>8.291056462193868</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>10.47916992313484</v>
+        <v>10.46369011212482</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>24.78261312238272</v>
+        <v>24.65646268449581</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>6.007656157910541</v>
+        <v>5.984598659701445</v>
       </c>
     </row>
     <row r="53">
@@ -3878,13 +4472,13 @@
         <v>7.159659825023882</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>8.200068097109837</v>
+        <v>8.173177487448003</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>18.53277563490452</v>
+        <v>18.31363457551492</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>5.762688664292432</v>
+        <v>5.722634545820449</v>
       </c>
     </row>
     <row r="54">
@@ -3905,13 +4499,13 @@
         <v>9.505463270105125</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>12.09441607894449</v>
+        <v>12.08675917973447</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>26.10193828613697</v>
+        <v>26.03953951475823</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>8.140550498743243</v>
+        <v>8.129145389229436</v>
       </c>
     </row>
     <row r="55">
@@ -3932,13 +4526,13 @@
         <v>7.597789138311</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>8.026176147807087</v>
+        <v>8.034199112807419</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>16.46987210812729</v>
+        <v>16.53525407870098</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>5.932505891907098</v>
+        <v>5.944456263976051</v>
       </c>
     </row>
     <row r="56">
@@ -3959,13 +4553,13 @@
         <v>10.18051031759922</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>11.94804521561416</v>
+        <v>12.02038132415104</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>23.86210666582826</v>
+        <v>24.45159911900207</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>8.589691572773852</v>
+        <v>8.697437700421187</v>
       </c>
     </row>
     <row r="57">
@@ -3986,13 +4580,13 @@
         <v>10.30108817662384</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.10303840070217</v>
+        <v>14.19731834978697</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>28.53357944700941</v>
+        <v>29.3018999939014</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>8.000202076053485</v>
+        <v>8.140634007410352</v>
       </c>
     </row>
     <row r="58">
@@ -4013,13 +4607,13 @@
         <v>8.597275720579407</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>10.8906094859625</v>
+        <v>11.11144444186224</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>23.92814001207431</v>
+        <v>25.72780193103825</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>6.051915170269139</v>
+        <v>6.380853398059418</v>
       </c>
     </row>
     <row r="59">
@@ -4040,13 +4634,13 @@
         <v>7.430207131165736</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>8.578925164964984</v>
+        <v>8.770016449215845</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>17.75355010778787</v>
+        <v>19.31082035927971</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>5.877181834650112</v>
+        <v>6.161816249213457</v>
       </c>
     </row>
     <row r="60">
@@ -4067,13 +4661,13 @@
         <v>10.04362681377087</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>12.68541195666362</v>
+        <v>13.02129592835208</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>24.29661103517065</v>
+        <v>27.03384794848117</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8.243744040919578</v>
+        <v>8.744050153872639</v>
       </c>
     </row>
     <row r="61">
@@ -4094,13 +4688,13 @@
         <v>7.536230387940945</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>7.868705170235595</v>
+        <v>7.799482319555394</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>16.58070068557419</v>
+        <v>16.01657926836595</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5.849812237916688</v>
+        <v>5.74670337214603</v>
       </c>
     </row>
     <row r="62">
@@ -4121,13 +4715,13 @@
         <v>9.911975514681115</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>11.69756954939043</v>
+        <v>11.62843875696725</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>24.52433650686949</v>
+        <v>23.96096530485618</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>8.513615784526946</v>
+        <v>8.41064404143143</v>
       </c>
     </row>
     <row r="63">
@@ -4148,13 +4742,13 @@
         <v>10.30615284449264</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>13.57658127581013</v>
+        <v>13.47206873271256</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>28.1686541392487</v>
+        <v>27.31694457587614</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7.736200844743403</v>
+        <v>7.580527253267352</v>
       </c>
     </row>
     <row r="64">
@@ -4175,13 +4769,13 @@
         <v>8.138027219521938</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>10.19513511339303</v>
+        <v>10.02639120686015</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>25.18560220101469</v>
+        <v>23.81044860992156</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>5.953343834371023</v>
+        <v>5.701996300466422</v>
       </c>
     </row>
     <row r="65">
@@ -4202,13 +4796,13 @@
         <v>6.973182554530692</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>7.919057071066465</v>
+        <v>7.735163685823844</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>19.01550105106669</v>
+        <v>17.51688901647217</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>5.668104134377691</v>
+        <v>5.394191139047716</v>
       </c>
     </row>
     <row r="66">
@@ -4229,13 +4823,13 @@
         <v>9.110295706004811</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>11.60389103202933</v>
+        <v>11.31883290234694</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>27.4213742530003</v>
+        <v>25.09833504668288</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>8.037399084106065</v>
+        <v>7.612799112544019</v>
       </c>
     </row>
   </sheetData>
@@ -4249,7 +4843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T44"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4265,13 +4859,17 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4400,22 +4998,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>382.1317787366347</v>
+        <v>381.0150238529766</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>375.7219392474648</v>
+        <v>375.6395710821145</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>421.980478094075</v>
+        <v>421.9776190609413</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>422.2037337233075</v>
+        <v>421.5800551253174</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>433.0236610262107</v>
+        <v>431.6036398623501</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>419.1639305686859</v>
+        <v>418.8985605046918</v>
       </c>
     </row>
     <row r="7">
@@ -4425,22 +5023,22 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>790.2398152649166</v>
+        <v>781.1389859657324</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>771.2996576642566</v>
+        <v>770.6284104429461</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>857.9924216597727</v>
+        <v>857.9691223907109</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>998.4866996564672</v>
+        <v>993.404122861038</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>978.666306104484</v>
+        <v>967.0940529604534</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>904.6316065250904</v>
+        <v>902.469012307805</v>
       </c>
     </row>
     <row r="8">
@@ -4450,890 +5048,842 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>282.8162050025537</v>
+        <v>281.1527755386359</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>272.0314129763893</v>
+        <v>271.9087238929229</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>238.9808310788453</v>
+        <v>238.9765724899441</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>242.0473071245772</v>
+        <v>241.1183249718299</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>304.3121731691063</v>
+        <v>302.1970223173678</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>282.1322767278143</v>
+        <v>281.737002536719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total cash costs</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>2404.903097611558</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>2259.716100702914</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2458.678259443044</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>2657.681065906678</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2729.96850250375</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>2498.948967350904</v>
+          <t>Sum of the five cash lines</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>B4+B5+B6+B7+B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="6">
+        <f>C4+C5+C6+C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="6">
+        <f>D4+D5+D6+D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>E4+E5+E6+E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>F4+F5+F6+F7+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>G4+G5+G6+G7+G8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adj EBITDA</t>
+          <t>less: D&amp;A add-back (the one add-back schedule)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2399.132402388442</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>918.391699297086</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>594.4510405569569</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1371.299634093322</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>2550.76399749625</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>966.8151326490954</v>
+        <v>20.63397059990752</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Adj EBITDA margin %</t>
+          <t>Total cash costs (net of the add-back)</t>
         </is>
       </c>
       <c r="B11" s="6">
-        <f>B10/B3*100</f>
+        <f>B9-B10</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>C10/C3*100</f>
+        <f>C9-C10</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>D10/D3*100</f>
+        <f>D9-D10</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>E10/E3*100</f>
+        <f>E9-E10</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>F10/F3*100</f>
+        <f>F9-F10</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>G10/G3*100</f>
+        <f>G9-G10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  80% band low %</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>47.85967437231024</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>26.29758634866444</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>15.58174442883745</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>30.14741766310557</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>44.4147458627971</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>24.00768380879198</v>
+          <t>Adj EBITDA</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>B3-B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="6">
+        <f>C3-C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="6">
+        <f>D3-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="6">
+        <f>E3-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="6">
+        <f>F3-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>G3-G11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  80% band high %</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>52.02020380046522</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>31.49728765133557</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>23.35869877852733</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>37.92437201279545</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>52.19170021248697</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>31.78463815848187</v>
+          <t>Adj EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
+        <f>B12/B3*100</f>
+        <v/>
+      </c>
+      <c r="C13" s="6">
+        <f>C12/C3*100</f>
+        <v/>
+      </c>
+      <c r="D13" s="6">
+        <f>D12/D3*100</f>
+        <v/>
+      </c>
+      <c r="E13" s="6">
+        <f>E12/E3*100</f>
+        <v/>
+      </c>
+      <c r="F13" s="6">
+        <f>F12/F3*100</f>
+        <v/>
+      </c>
+      <c r="G13" s="6">
+        <f>G12/G3*100</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t xml:space="preserve">  80% band low %</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>451.5791856610708</v>
+        <v>47.85967437231024</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>465.1605145531331</v>
+        <v>26.4812578089992</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>464.0287371454613</v>
+        <v>15.81999842391128</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>551.1755975361942</v>
+        <v>30.3856716581794</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>511.0871201060549</v>
+        <v>44.65299985787093</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>526.4581613122519</v>
+        <v>24.24593780386581</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
+          <t xml:space="preserve">  80% band high %</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>52.02020380046522</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>31.3136161910008</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>23.1204447834535</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>37.68611801772163</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>51.95344621741314</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>20.63397059990752</v>
+        <v>31.54638416340804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GAAP operating income</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>B10-B15-B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="6">
-        <f>C10-C15-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="6">
-        <f>D10-D15-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
-        <f>E10-E15-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="6">
-        <f>F10-F15-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="6">
-        <f>G10-G15-G14</f>
-        <v/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>451.5791856610708</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>465.1605145531331</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>464.0287371454613</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>551.1755975361942</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>511.0871201060549</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>526.4581613122519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GAAP operating margin %</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>B16/B3*100</f>
-        <v/>
-      </c>
-      <c r="C17" s="6">
-        <f>C16/C3*100</f>
-        <v/>
-      </c>
-      <c r="D17" s="6">
-        <f>D16/D3*100</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
-        <f>E16/E3*100</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>F16/F3*100</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>G16/G3*100</f>
-        <v/>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>20.63397059990752</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>183.6651628209243</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>169.8969404377947</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>185.056467449014</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>208.2425784616941</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>196.2287312110724</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>175.7070731323778</v>
+          <t>GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>B12-B17-B16</f>
+        <v/>
+      </c>
+      <c r="C18" s="6">
+        <f>C12-C17-C16</f>
+        <v/>
+      </c>
+      <c r="D18" s="6">
+        <f>D12-D17-D16</f>
+        <v/>
+      </c>
+      <c r="E18" s="6">
+        <f>E12-E17-E16</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>F12-F17-F16</f>
+        <v/>
+      </c>
+      <c r="G18" s="6">
+        <f>G12-G17-G16</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>37</v>
+          <t>GAAP operating margin %</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>B18/B3*100</f>
+        <v/>
+      </c>
+      <c r="C19" s="6">
+        <f>C18/C3*100</f>
+        <v/>
+      </c>
+      <c r="D19" s="6">
+        <f>D18/D3*100</f>
+        <v/>
+      </c>
+      <c r="E19" s="6">
+        <f>E18/E3*100</f>
+        <v/>
+      </c>
+      <c r="F19" s="6">
+        <f>F18/F3*100</f>
+        <v/>
+      </c>
+      <c r="G19" s="6">
+        <f>G18/G3*100</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>183.6651628209243</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>169.8969404377947</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>185.056467449014</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>208.2425784616941</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>196.2287312110724</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3.707412112603224</v>
+        <v>175.7070731323778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pretax income</t>
-        </is>
-      </c>
-      <c r="B21" s="6">
-        <f>B16+B18-B19+B20</f>
-        <v/>
-      </c>
-      <c r="C21" s="6">
-        <f>C16+C18-C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="6">
-        <f>D16+D18-D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="6">
-        <f>E16+E18-E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="6">
-        <f>F16+F18-F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="6">
-        <f>G16+G18-G19+G20</f>
-        <v/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Effective tax rate %</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>18</v>
+        <v>3.707412112603224</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>18</v>
+        <v>3.707412112603224</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>17.5</v>
+        <v>3.707412112603224</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>17.5</v>
+        <v>3.707412112603224</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>17.5</v>
+        <v>3.707412112603224</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>17.5</v>
+        <v>3.707412112603224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tax provision</t>
+          <t>Pretax income</t>
         </is>
       </c>
       <c r="B23" s="6">
-        <f>B21*B22/100</f>
+        <f>B18+B20-B21+B22</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>C21*C22/100</f>
+        <f>C18+C20-C21+C22</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>D21*D22/100</f>
+        <f>D18+D20-D21+D22</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>E21*E22/100</f>
+        <f>E18+E20-E21+E22</f>
         <v/>
       </c>
       <c r="F23" s="6">
-        <f>F21*F22/100</f>
+        <f>F18+F20-F21+F22</f>
         <v/>
       </c>
       <c r="G23" s="6">
-        <f>G21*G22/100</f>
+        <f>G18+G20-G21+G22</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B24" s="6">
-        <f>B21-B23</f>
-        <v/>
-      </c>
-      <c r="C24" s="6">
-        <f>C21-C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="6">
-        <f>D21-D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>E21-E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="6">
-        <f>F21-F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="6">
-        <f>G21-G23</f>
-        <v/>
+          <t>Effective tax rate %</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Diluted shares (m)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>591.6758133819055</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>586.3516267638111</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>581.0274401457166</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>575.7032535276221</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>570.3790669095276</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>565.0548802914333</v>
+          <t>Tax provision</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>B23*B24/100</f>
+        <v/>
+      </c>
+      <c r="C25" s="6">
+        <f>C23*C24/100</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>D23*D24/100</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>E23*E24/100</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>F23*F24/100</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>G23*G24/100</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EPS, diluted (GAAP = Street definition)</t>
+          <t>Net income</t>
         </is>
       </c>
       <c r="B26" s="6">
-        <f>B24/B25</f>
+        <f>B23-B25</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>C24/C25</f>
+        <f>C23-C25</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>D24/D25</f>
+        <f>D23-D25</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>E24/E25</f>
+        <f>E23-E25</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>F24/F25</f>
+        <f>F23-F25</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>G24/G25</f>
+        <f>G23-G25</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EPS 80% band low</t>
+          <t>Diluted shares (m)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>2.740404794660193</v>
+        <v>591.6758133819055</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.6804652708035136</v>
+        <v>586.3516267638111</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.202806911357602</v>
+        <v>581.0274401457166</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1.171894716094297</v>
+        <v>575.7032535276221</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2.859023492727179</v>
+        <v>570.3790669095276</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.6239782104601869</v>
+        <v>565.0548802914333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EPS 80% band high</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>3.017408030352287</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>0.911566757027642</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>0.5399482850364905</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>1.620908839253096</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>3.45303394688974</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>1.017502792927981</v>
+          <t>EPS, diluted (GAAP = Street definition)</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>B26/B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="6">
+        <f>C26/C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="6">
+        <f>D26/D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
+        <f>E26/E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="6">
+        <f>F26/F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="6">
+        <f>G26/G27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Capex</t>
+          <t xml:space="preserve">  EPS 80% band low</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>2.704270016741174</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>0.6448629972349915</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>0.1807058348737482</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>1.160327207081948</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>2.857618570081216</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>8.929320995781959</v>
+        <v>0.6075936178499651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CFO (DIAGNOSTIC — quarterly FCF failed its backtest)</t>
+          <t xml:space="preserve">  EPS 80% band high</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1001.158676867313</v>
+        <v>3.053542808271305</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>889.8846545931908</v>
+        <v>0.9471690305961642</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1824.066140198401</v>
+        <v>0.5620493615203443</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1500.211805542739</v>
+        <v>1.632476348265445</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1044.183135602645</v>
+        <v>3.454438869535703</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>950.1638541449172</v>
+        <v>1.033887385538203</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>8.929320995781959</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CFO (DIAGNOSTIC — quarterly FCF failed its backtest)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1016.856577360912</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>887.9493910365632</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1824.519426575492</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1502.50084013535</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1066.018092085144</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>939.3845711981828</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>FCF (DIAGNOSTIC — do not quote quarterly)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>992.2293558715312</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>880.9553335974089</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>1815.136819202619</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>1491.282484546957</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>1035.253814606862</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>941.2345331491352</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="B33" s="6" t="n">
+        <v>1007.927256365131</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>879.0200700407812</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1815.590105579709</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1493.571519139568</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1057.088771089362</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>930.4552502024007</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Annual forecast — FY26 / FY27 / FY28, three revenue scenarios (FY26 = 1H26 actual + 3Q26 combination + 4Q26 Street)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>revenue_musd</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>adj_ebitda_musd</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>adj_ebitda_margin_pct</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>sbc_musd</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>da_musd</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>op_income_musd</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>op_margin_pct</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>interest_income_musd</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>interest_expense_musd</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>pretax_income_musd</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>tax_provision_musd</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>tax_rate_pct</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>net_income_musd</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>ni_basis</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>m7_annual_net_income_musd</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>diluted_shares_m</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>eps_diluted</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>cfo_musd</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>fcf_musd_range_mid</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>fcf_musd_bias_adjusted</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>fcf_margin_pct</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>14268.1434</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>5097.524101685529</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>35.72661108582304</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>1813.739700214204</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>80.26794119981503</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>3203.516460271509</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>22.45223061236901</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>691.5621032587189</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>3824.493387755434</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>17.7426269597819</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>3145.927792864462</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>595.7568600364291</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>5.280556555693033</v>
-      </c>
-      <c r="R36" s="4" t="n">
-        <v>4830.184689468942</v>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>4431.184689468942</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>33.85293064456404</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>FY27</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>15828.6067</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>5483.329804795625</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>34.64189810715067</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>2052.749616099962</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>82.53588239963007</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>3348.044306296033</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>21.15185732864304</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>765.2348502541582</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>3980.108805000604</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>3283.589764125499</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>573.0411602185749</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>5.730111538363214</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>5282.907651505574</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>4883.907651505574</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>33.37569598912059</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>FY28</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -5343,201 +5893,243 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>FY27 margin rolled flat onto FY28 base revenue (M6 R15 rule); NOT a forecast</t>
+          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>17137.441</v>
+        <v>14268.1434</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5936.734849393063</v>
+        <v>5097.524101685529</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>34.64189810715067</v>
+        <v>35.72661108582304</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2323.255639109014</v>
+        <v>1813.739700214204</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>82.53588239963007</v>
+        <v>80.26794119981504</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3530.943327884419</v>
+        <v>3203.516460271509</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>20.60367897333341</v>
+        <v>22.45223061236901</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>794.5100425825694</v>
+        <v>691.5621032587189</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>4192.283018917401</v>
+        <v>3824.493387755435</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>17.5</v>
+        <v>678.3688097959782</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>3458.633490606856</v>
+        <v>17.73748156992128</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>551.7444137461971</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>6.268542833308739</v>
+        <v>3146.124577959456</v>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>sum of quarters (1H26 actual + 3Q26/4Q26 forecast)</t>
+        </is>
       </c>
       <c r="R38" s="4" t="n">
-        <v>5715.86253559194</v>
+        <v>3208.821035116772</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>5316.86253559194</v>
+        <v>595.7568600364291</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>33.35306908185382</v>
+        <v>5.2808868667783</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>4882.805968397476</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>4843.947326405912</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>4444.947326405912</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>33.94938774168693</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
+          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>14164.807</v>
+        <v>15828.6067</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5057.344263384326</v>
+        <v>5483.329804795625</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>35.70358751364792</v>
+        <v>34.64189810715067</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1813.739700214204</v>
+        <v>2052.749616099962</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>80.26794119981503</v>
+        <v>82.53588239963008</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>3163.336621970307</v>
+        <v>3348.044306296033</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>22.33236656150914</v>
+        <v>21.15185732864304</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>689.2842876263994</v>
+        <v>765.2348502541582</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>3782.035733821912</v>
+        <v>3980.108805000604</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>17.74247658859565</v>
+        <v>696.5190408751056</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>3111.008929176237</v>
+        <v>17.5</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>595.7568600364291</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>5.221943947042434</v>
+        <v>3283.589764125499</v>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>sum of the four forecast quarters</t>
+        </is>
       </c>
       <c r="R39" s="4" t="n">
-        <v>4820.113594108805</v>
+        <v>3348.637452508412</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>4421.113594108805</v>
+        <v>573.0411602185749</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>34.02879823289371</v>
+        <v>5.730111538363214</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>5332.422929994169</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>5296.705646011041</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>4897.705646011041</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>33.46286724030512</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
+          <t>FY27 margin rolled flat onto FY28 base revenue (M6 R15 rule); NOT a forecast</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>14948.3339</v>
+        <v>17137.441</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5158.581575823143</v>
+        <v>5936.734849393063</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>34.5094082747452</v>
+        <v>34.64189810715067</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2052.749616099962</v>
+        <v>2323.255639109014</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>82.53588239963007</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>3023.29607732355</v>
+        <v>3530.943327884419</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>20.22497020436204</v>
+        <v>20.60367897333341</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>742.9386984942925</v>
+        <v>794.5100425825694</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>148</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>3633.064424268256</v>
+        <v>4192.283018917401</v>
       </c>
       <c r="N40" s="4" t="n">
+        <v>733.6495283105451</v>
+      </c>
+      <c r="O40" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="O40" s="4" t="n">
-        <v>2997.278150021311</v>
-      </c>
       <c r="P40" s="4" t="n">
-        <v>573.0411602185749</v>
-      </c>
-      <c r="Q40" s="4" t="n">
-        <v>5.230476199786522</v>
+        <v>3458.633490606856</v>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>annual ETR on annual pretax (no quarterly build for this period)</t>
+        </is>
       </c>
       <c r="R40" s="4" t="n">
-        <v>4961.344502950717</v>
+        <v>3529.059867343592</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>4562.344502950717</v>
+        <v>551.7444137461971</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>33.18994970369719</v>
+        <v>6.268542833308739</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>5766.518747973769</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>5730.801463990641</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>5331.801463990641</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>33.4402403718889</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FY28</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -5547,263 +6139,483 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>FY27 margin rolled flat onto FY28 base revenue (M6 R15 rule); NOT a forecast</t>
+          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>17137.441</v>
+        <v>14164.807</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5914.029482533578</v>
+        <v>5017.187679811765</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>34.5094082747452</v>
+        <v>35.42009206205044</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2323.255639109014</v>
+        <v>1813.739700214204</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>82.53588239963007</v>
+        <v>80.26794119981504</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3508.237961024933</v>
+        <v>3123.180038397745</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>20.47118914092794</v>
+        <v>22.04887110991167</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>792.6785828393811</v>
+        <v>689.2842876263995</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>4167.746192314727</v>
+        <v>3741.879150249352</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>17.5</v>
+        <v>663.4982470448832</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>3438.390608659649</v>
+        <v>17.73168561578663</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>551.7444137461971</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>6.231853958092473</v>
+        <v>3078.380903204468</v>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>sum of quarters (1H26 actual + 3Q26/4Q26 forecast)</t>
+        </is>
       </c>
       <c r="R41" s="4" t="n">
-        <v>5691.646214444324</v>
+        <v>3206.953226298269</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>5292.646214444324</v>
+        <v>595.7568600364291</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>33.21176256387593</v>
+        <v>5.167176594519168</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>4847.038845402056</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>4808.180203410492</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>4409.180203410492</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>33.94455147472529</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>bull</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
+          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>14391.9366</v>
+        <v>14948.3339</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5148.861174018934</v>
+        <v>4805.364117983128</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>35.77601345199738</v>
+        <v>32.14648635847724</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1813.739700214204</v>
+        <v>2052.749616099962</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>80.26794119981503</v>
+        <v>82.53588239963008</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>3254.853532604915</v>
+        <v>2670.078619483536</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>22.61581344518232</v>
+        <v>17.86204828809408</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>693.8837962728763</v>
+        <v>742.9386984942926</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>3878.152153102998</v>
+        <v>3279.846966428242</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>17.74278004694994</v>
+        <v>573.9732191249423</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>3190.06014669188</v>
+        <v>17.5</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>595.7568600364291</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>5.354634349484142</v>
+        <v>2705.873747303299</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>sum of the four forecast quarters</t>
+        </is>
       </c>
       <c r="R42" s="4" t="n">
-        <v>4853.486136168656</v>
+        <v>3330.243127306522</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>4454.486136168656</v>
+        <v>573.0411602185749</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>33.72364867260919</v>
+        <v>4.721953561365816</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>4776.286318791484</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>4740.569034808355</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>4341.569034808355</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>31.71302612399068</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>bull</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
+          <t>FY27 margin rolled flat onto FY28 base revenue (M6 R15 rule); NOT a forecast</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>16570.7437</v>
+        <v>17137.441</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5751.588277590047</v>
+        <v>5509.085133257085</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>34.7092947770959</v>
+        <v>32.14648635847724</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2052.749616099962</v>
+        <v>2323.255639109014</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>82.53588239963007</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3616.302779090455</v>
+        <v>3103.29361174844</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>21.82341869840432</v>
+        <v>18.10826722465998</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>784.5969724998841</v>
+        <v>792.6785828393811</v>
       </c>
       <c r="L43" s="4" t="n">
         <v>148</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>4267.729400040752</v>
+        <v>3762.801843038234</v>
       </c>
       <c r="N43" s="4" t="n">
+        <v>658.4903225316909</v>
+      </c>
+      <c r="O43" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="O43" s="4" t="n">
-        <v>3520.87675503362</v>
-      </c>
       <c r="P43" s="4" t="n">
-        <v>573.0411602185749</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>6.144195215733986</v>
+        <v>3104.311520506544</v>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>annual ETR on annual pretax (no quarterly build for this period)</t>
+        </is>
       </c>
       <c r="R43" s="4" t="n">
-        <v>5524.089093996957</v>
+        <v>3527.548913055462</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>5125.089093996957</v>
+        <v>551.7444137461971</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>33.3363981364153</v>
+        <v>5.626357862744994</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>5412.196777873457</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>5376.479493890329</v>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>4977.479493890329</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>31.37270899366089</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>1H26 actual + 3Q26 combination + 4Q26 Street</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>14391.9366</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>5194.930799887501</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>36.09612065611449</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>1813.739700214204</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>80.26794119981504</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>3300.923158473483</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>22.93592064929943</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>693.8837962728763</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>3924.221778971566</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>696.3199202148818</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>17.74415309415486</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>3227.901858756684</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>sum of quarters (1H26 actual + 3Q26/4Q26 forecast)</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>3210.724823388381</v>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>595.7568600364291</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>5.418153067611014</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>4934.643835289403</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>4895.785193297839</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>4496.785193297839</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>34.01755670114499</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>sum of the four 2027 combination quarters (SCENARIO: h&gt;=2 fails its test)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>16570.7437</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>6052.893039907587</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>36.52758831764194</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>2052.749616099962</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>82.53588239963008</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>3917.607541407995</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>23.64171223895036</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>784.5969724998841</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>4569.034162358292</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>799.5809784127011</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>3769.453183945591</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>sum of the four forecast quarters</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>3364.611203361136</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>573.0411602185749</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>6.57797981301694</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>5775.2355686585</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>5739.518284675371</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>5340.518284675371</v>
+      </c>
+      <c r="X45" s="4" t="n">
+        <v>34.63645560262556</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>FY28</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>bull</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>FY27 margin rolled flat onto FY28 base revenue (M6 R15 rule); NOT a forecast</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D46" s="4" t="n">
         <v>17137.441</v>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>5948.284913940891</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>34.7092947770959</v>
-      </c>
-      <c r="G44" s="4" t="n">
+      <c r="E46" s="4" t="n">
+        <v>6259.893896658779</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>36.52758831764194</v>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>2323.255639109014</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>82.53588239963007</v>
       </c>
-      <c r="I44" s="4" t="n">
-        <v>3542.493392432246</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>20.67107564327864</v>
-      </c>
-      <c r="K44" s="4" t="n">
+      <c r="I46" s="4" t="n">
+        <v>3854.102375150135</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>22.48936918382467</v>
+      </c>
+      <c r="K46" s="4" t="n">
         <v>796.6017585980471</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L46" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="M44" s="4" t="n">
-        <v>4205.924799480706</v>
-      </c>
-      <c r="N44" s="4" t="n">
+      <c r="M46" s="4" t="n">
+        <v>4517.533782198595</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>790.5684118847539</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="O44" s="4" t="n">
-        <v>3469.887959571583</v>
-      </c>
-      <c r="P44" s="4" t="n">
+      <c r="P46" s="4" t="n">
+        <v>3726.965370313841</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>annual ETR on annual pretax (no quarterly build for this period)</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>3530.785533056362</v>
+      </c>
+      <c r="S46" s="4" t="n">
         <v>551.7444137461971</v>
       </c>
-      <c r="Q44" s="4" t="n">
-        <v>6.288940808683446</v>
-      </c>
-      <c r="R44" s="4" t="n">
-        <v>5729.138265852537</v>
-      </c>
-      <c r="S44" s="4" t="n">
-        <v>5330.138265852537</v>
-      </c>
-      <c r="T44" s="4" t="n">
-        <v>33.43053531651859</v>
+      <c r="T46" s="4" t="n">
+        <v>6.75487649255702</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>6034.850627680755</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>5999.133343697627</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>5600.133343697627</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>35.00600436026374</v>
       </c>
     </row>
   </sheetData>
@@ -9472,7 +10284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9485,12 +10297,13 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9553,30 +10366,35 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>lseg_sd_musd</t>
+          <t>lseg_revenue_sd_musd</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>lseg_ebitda_sd_musd</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>gap_ebitda_musd</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>gap_margin_pp</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>lseg_eps</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>bloomberg_ebitda_musd</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>gap_eps</t>
         </is>
@@ -9621,14 +10439,17 @@
         <v>24.27626</v>
       </c>
       <c r="L3" s="4" t="n">
+        <v>20.0425</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>37.61061238844241</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>0.1641917768859073</v>
       </c>
-      <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -9669,14 +10490,17 @@
         <v>48.55902</v>
       </c>
       <c r="L4" s="4" t="n">
+        <v>26.52396</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>4.707819297085962</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>-4.845632659566945e-07</v>
       </c>
-      <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9716,15 +10540,16 @@
       <c r="K5" s="4" t="n">
         <v>49.4461</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="4" t="n">
         <v>-16.28102944304317</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>-0.8176982587576553</v>
       </c>
-      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9764,15 +10589,16 @@
       <c r="K6" s="4" t="n">
         <v>120.0081</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="4" t="n">
         <v>-80.4146359066774</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>-1.924903852628532</v>
       </c>
-      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -9812,15 +10638,16 @@
       <c r="K7" s="4" t="n">
         <v>94.58991</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="4" t="n">
         <v>-144.7887725037494</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>-2.846103355994842</v>
       </c>
-      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -9860,15 +10687,16 @@
       <c r="K8" s="4" t="n">
         <v>72.37043</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="4" t="n">
         <v>-101.5809473509046</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>-2.379285151805515</v>
       </c>
-      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -9891,7 +10719,7 @@
         <v>35.72661108582304</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.280556555693033</v>
+        <v>5.2808868667783</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>14189.55705</v>
@@ -9906,22 +10734,25 @@
         <v>44</v>
       </c>
       <c r="K9" s="4" t="n">
+        <v>59.21929</v>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>40.21549</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>43.80196168552902</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>0.1108260250765553</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>5.31259</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>5046.838</v>
       </c>
-      <c r="P9" s="4" t="n">
-        <v>-0.0320334443069674</v>
+      <c r="Q9" s="4" t="n">
+        <v>-0.0317031332216997</v>
       </c>
     </row>
     <row r="10">
@@ -9960,19 +10791,22 @@
         <v>44</v>
       </c>
       <c r="K10" s="4" t="n">
+        <v>258.17766</v>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>154.22275</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>-282.7693652043754</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>-1.807785931612002</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>6.22753</v>
       </c>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="4" t="n">
         <v>-0.4974184616367862</v>
       </c>
     </row>
@@ -10012,19 +10846,22 @@
         <v>26</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>513.94985</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>271.9227</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>-665.9825006069368</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>-3.012401087524317</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>7.51977</v>
       </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="4" t="n">
         <v>-1.251227166691261</v>
       </c>
     </row>
@@ -10702,7 +11539,7 @@
         <v>20.44594139352468</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>30.2909459974662</v>
+        <v>30.04363280324104</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>51.76309493232024</v>
@@ -10733,7 +11570,7 @@
         <v>27.12851231430345</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>44.65087716307517</v>
+        <v>44.62330401183948</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>29.75432624874153</v>
@@ -10764,7 +11601,7 @@
         <v>31.4558874431343</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>49.75071743056191</v>
+        <v>49.74972117759954</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>17.4232559804365</v>
@@ -10795,7 +11632,7 @@
         <v>25.37149243600001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>41.26943920342809</v>
+        <v>41.10475145632208</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>33.58671282879953</v>
@@ -10826,7 +11663,7 @@
         <v>19.87807104342979</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>32.49553239630678</v>
+        <v>32.20944660878337</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>51.76309493232024</v>
@@ -10857,7 +11694,7 @@
         <v>26.44376062991696</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>46.33690486382471</v>
+        <v>46.25544408372214</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>29.75432624874153</v>
@@ -12291,37 +13128,37 @@
         <v>13</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1.962253686422445</v>
+        <v>1.951983093583188</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1.567076338152753</v>
+        <v>1.560214021478974</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2.363169742468254</v>
+        <v>2.349148333857344</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.4420676195151281</v>
+        <v>-0.450166606954569</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.8348885480605513</v>
+        <v>0.8305186745815915</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.8102164834520201</v>
+        <v>0.806668499254698</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.5014835863728655</v>
+        <v>0.4988587811466886</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>1.19563216737966</v>
+        <v>1.189374132925887</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.25183415623047</v>
+        <v>1.246352303053341</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>-1.030655905903281</v>
+        <v>-1.076682684667773</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.3027022092948048</v>
+        <v>0.2816220505794327</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9</v>
@@ -12363,46 +13200,46 @@
         <v>12</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.255370354078833</v>
+        <v>2.228944080178042</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.893181234566952</v>
+        <v>1.862095709247065</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2.582588934842889</v>
+        <v>2.549134646349621</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.4615550173883957</v>
+        <v>-0.442768154280881</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.9102159037952789</v>
+        <v>0.8995508639099009</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>0.9661711636375916</v>
+        <v>0.9503068936869808</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.6212558102101102</v>
+        <v>0.6139765284844375</v>
       </c>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="4" t="n">
-        <v>-0.6452044921312529</v>
+        <v>-0.7281506586805081</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.5187946755008714</v>
+        <v>0.4665213661392766</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>12</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>0.38720703125</v>
+        <v>0.61279296875</v>
       </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="U37" s="4" t="n">
         <v>0.8333333333333334</v>
@@ -12501,37 +13338,37 @@
         <v>9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.275484015232669</v>
+        <v>1.26912380855547</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.291377370744437</v>
+        <v>1.283541346512894</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1.485669487636973</v>
+        <v>1.474162122634583</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.2222709956297267</v>
+        <v>0.2269222839235085</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.8080968159910443</v>
+        <v>0.8040672376478366</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8064447148685795</v>
+        <v>0.801551241844914</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.3640020219400458</v>
+        <v>0.3621869242494373</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>1.284528090858962</v>
+        <v>1.278122785858695</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1.333030287289093</v>
+        <v>1.324941514890552</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>-0.7437252727502091</v>
+        <v>-0.7619711565601504</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>0.4570426966690255</v>
+        <v>0.4460772191449527</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>6</v>
@@ -12573,33 +13410,33 @@
         <v>8</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1.761819257437431</v>
+        <v>1.765683027396108</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1.710820391571186</v>
+        <v>1.714804718610076</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1.936910485506824</v>
+        <v>1.939734607897329</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.4262147177582265</v>
+        <v>0.4240406162222707</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1.023780916693291</v>
+        <v>1.02602612654299</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.028753095838894</v>
+        <v>1.031148957377771</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.5726066151716199</v>
+        <v>0.5738623740858788</v>
       </c>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
       <c r="N40" s="4" t="n">
-        <v>0.1269957091203731</v>
+        <v>0.1387231968078926</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.8989437946784413</v>
+        <v>0.8896688869302445</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>3</v>
@@ -12711,37 +13548,37 @@
         <v>13</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>75.29294052323506</v>
+        <v>75.46918536475431</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>70.42004595891721</v>
+        <v>70.58891881366988</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>85.79466672164526</v>
+        <v>86.31885928503564</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-6.458075237173878</v>
+        <v>-6.198149854358816</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.5774679804141922</v>
+        <v>0.5788197107621275</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.5990954734323608</v>
+        <v>0.6005321518879094</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.5833183711573634</v>
+        <v>0.5846837960320657</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>1.149579868148309</v>
+        <v>1.152270791364583</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1.215549590674978</v>
+        <v>1.218464574990531</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>-1.969653613322125</v>
+        <v>-1.955720711144799</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.048878082645658</v>
+        <v>0.0504980635707033</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9</v>
@@ -12783,33 +13620,33 @@
         <v>12</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>85.78944086927048</v>
+        <v>86.38587021580661</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>85.76838486226809</v>
+        <v>86.20300744214747</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>99.01257343450094</v>
+        <v>99.54472150175688</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>8.66068460655022</v>
+        <v>10.09226734645174</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.6486914243423099</v>
+        <v>0.6532012870760424</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.7283266848434904</v>
+        <v>0.7320174063520044</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.7487078475863606</v>
+        <v>0.7539130491561304</v>
       </c>
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="n"/>
       <c r="N43" s="4" t="n">
-        <v>-1.162800867343936</v>
+        <v>-1.138866621443014</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.2449103051849408</v>
+        <v>0.2547587893633087</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>8</v>
@@ -12921,37 +13758,37 @@
         <v>9</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>68.95397876383683</v>
+        <v>68.50241698998701</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>67.31637065654289</v>
+        <v>66.87492521553908</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>83.89337595611248</v>
+        <v>83.57273906920126</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>8.51047698451217</v>
+        <v>9.006609681859736</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.7605218246011415</v>
+        <v>0.7555413638601508</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>0.6469261108606806</v>
+        <v>0.6426837166329399</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.6672965686822919</v>
+        <v>0.6629266160321324</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>1.475360415718172</v>
+        <v>1.46569866191755</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>1.324596717631494</v>
+        <v>1.315910313767708</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>-1.150570921910478</v>
+        <v>-1.164197840621325</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.2499088014083275</v>
+        <v>0.2443438451485222</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>5</v>
@@ -12993,33 +13830,33 @@
         <v>8</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>92.95917742884475</v>
+        <v>93.6572226734344</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>88.14108841179703</v>
+        <v>88.99023884263318</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>107.9416987609984</v>
+        <v>108.4032606086686</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>19.7733010194093</v>
+        <v>19.68746395252231</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1.003607853482804</v>
+        <v>1.011144104436539</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.834695560462603</v>
+        <v>0.8427370097747829</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1.207262044530451</v>
+        <v>1.21632756718746</v>
       </c>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n"/>
       <c r="N46" s="4" t="n">
-        <v>0.0132711628786784</v>
+        <v>0.0413071277732203</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.9894114548518528</v>
+        <v>0.9670510507805974</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>5</v>
@@ -13947,9 +14784,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
@@ -14039,17 +14876,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2299 - 2499</t>
+          <t>2337 - 2462</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Street 2362 (n 36, sd 20.0)</t>
+          <t>Street 2362 (n 36, EBITDA sd 20.0)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>margin x bridge v3 revenue 4,804</t>
+          <t>final-margin|combined_dollar_from_margin (the margin combination x bridge-v3 revenue 4,804), band = its OWN conformal qhat80 62.6 on the 2024Q1+ calibration; W1/W2 h=0 MAE 30.7 / 25.8. Cross-check: the four-member dollar combination reads 2411</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14919,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.7654418391009807</v>
+        <v>0.7794080869036119</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -14093,7 +14930,7 @@
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Gaussian on the conformal sd; the 80% band contains the Street</t>
+          <t>Gaussian, sd = qhat80/1.2816 = 48.8, on the SAME object as the band (WS31 audit 04). The previously published 0.77 mixed a band from the margin route with an sd from the four-member dollar object and is withdrawn. Descriptive, not a validated probability: the calibration pool is n=10 and the object was selected after seeing the scoreboard</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14952,7 @@
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>Gaussian on the margin object's own conformal sd; same caveat</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14972,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2.74 - 3.02</t>
+          <t>2.70 - 3.05</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -14145,7 +14982,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>M7 bridge, ETR 18.0%, 591.7m shares; $0.001386 of EPS per $M of EBITDA</t>
+          <t>M7 bridge, ETR 18.0%, 591.7m shares; $0.001386 of EPS per $M of EBITDA. Band is JOINT (WS31 audit 06): EBITDA conformal term and M7's measured bridge sd $0.083 in quadrature, not EBITDA-only</t>
         </is>
       </c>
     </row>
@@ -14651,10 +15488,15 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>q4_margin_reading</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>pp_of_q4_per_1pp_of_q3</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>pp_of_q4_per_1pp_of_fy</t>
         </is>
@@ -14679,10 +15521,15 @@
       <c r="F27" s="4" t="n">
         <v>28.69623774247054</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>lower bound on 4Q26 (the FY sentence is a floor)</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14705,10 +15552,15 @@
       <c r="F28" s="4" t="n">
         <v>27.87997242573082</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>lower bound on 4Q26 (the FY sentence is a floor)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14731,10 +15583,15 @@
       <c r="F29" s="4" t="n">
         <v>27.66079007216181</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>lower bound on 4Q26 (the FY sentence is a floor)</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14757,10 +15614,15 @@
       <c r="F30" s="4" t="n">
         <v>27.03347506022294</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>lower bound on 4Q26 (the FY sentence is a floor)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14783,10 +15645,15 @@
       <c r="F31" s="4" t="n">
         <v>29.8186149790136</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14809,10 +15676,15 @@
       <c r="F32" s="4" t="n">
         <v>29.00234966227389</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14835,10 +15707,15 @@
       <c r="F33" s="4" t="n">
         <v>28.78316730870487</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14861,10 +15738,15 @@
       <c r="F34" s="4" t="n">
         <v>28.15585229676601</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14887,10 +15769,15 @@
       <c r="F35" s="4" t="n">
         <v>30.94099221555669</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14913,10 +15800,15 @@
       <c r="F36" s="4" t="n">
         <v>30.12472689881698</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14939,10 +15831,15 @@
       <c r="F37" s="4" t="n">
         <v>29.90554454524796</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14965,10 +15862,15 @@
       <c r="F38" s="4" t="n">
         <v>29.2782295333091</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -14991,10 +15893,15 @@
       <c r="F39" s="4" t="n">
         <v>32.06336945209976</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15017,10 +15924,15 @@
       <c r="F40" s="4" t="n">
         <v>31.24710413536004</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="I40" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15043,10 +15955,15 @@
       <c r="F41" s="4" t="n">
         <v>31.02792178179103</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15069,10 +15986,15 @@
       <c r="F42" s="4" t="n">
         <v>30.40060676985216</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15095,10 +16017,15 @@
       <c r="F43" s="4" t="n">
         <v>33.18574668864285</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15121,10 +16048,15 @@
       <c r="F44" s="4" t="n">
         <v>32.36948137190313</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="I44" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15147,10 +16079,15 @@
       <c r="F45" s="4" t="n">
         <v>32.15029901833412</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
@@ -15173,10 +16110,15 @@
       <c r="F46" s="4" t="n">
         <v>31.52298400639525</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>equality if the FY sentence is a point/'approximately' statement</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>-1.511602438406904</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>4.48950894617231</v>
       </c>
     </row>
